--- a/database/schema/temp.xlsx
+++ b/database/schema/temp.xlsx
@@ -9,13 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10455" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
     <sheet name="item_sort" sheetId="2" r:id="rId2"/>
     <sheet name="character" sheetId="3" r:id="rId3"/>
     <sheet name="race" sheetId="4" r:id="rId4"/>
+    <sheet name="race_subspecies" sheetId="6" r:id="rId5"/>
+    <sheet name="error" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="70">
   <si>
     <t>item</t>
   </si>
@@ -55,6 +57,18 @@
     <t>item_description</t>
   </si>
   <si>
+    <t>create_time</t>
+  </si>
+  <si>
+    <t>update_time</t>
+  </si>
+  <si>
+    <t>create_by</t>
+  </si>
+  <si>
+    <t>update_by</t>
+  </si>
+  <si>
     <t>物品表</t>
   </si>
   <si>
@@ -73,93 +87,114 @@
     <t>物品描述</t>
   </si>
   <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>更新人</t>
+  </si>
+  <si>
+    <t>bigint</t>
+  </si>
+  <si>
+    <t>char</t>
+  </si>
+  <si>
+    <t>varchar</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>item_sort</t>
+  </si>
+  <si>
+    <t>item_sort_code</t>
+  </si>
+  <si>
+    <t>item_sort_name</t>
+  </si>
+  <si>
+    <t>item_sort_description</t>
+  </si>
+  <si>
+    <t>物品分类表</t>
+  </si>
+  <si>
+    <t>物品分类编码</t>
+  </si>
+  <si>
+    <t>物品分类名称</t>
+  </si>
+  <si>
+    <t>物品分类描述</t>
+  </si>
+  <si>
+    <t>character</t>
+  </si>
+  <si>
+    <t>character_id</t>
+  </si>
+  <si>
+    <t>character_name</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>race_id</t>
+  </si>
+  <si>
+    <t>race_subsp_id</t>
+  </si>
+  <si>
+    <t>character_description</t>
+  </si>
+  <si>
+    <t>角色</t>
+  </si>
+  <si>
+    <t>角色_id</t>
+  </si>
+  <si>
+    <t>角色名称</t>
+  </si>
+  <si>
+    <t>角色性别</t>
+  </si>
+  <si>
+    <t>角色年龄</t>
+  </si>
+  <si>
+    <t>种族id</t>
+  </si>
+  <si>
+    <t>亚种id</t>
+  </si>
+  <si>
+    <t>角色描述</t>
+  </si>
+  <si>
+    <t>bool(tinyint(1))</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>smallint</t>
   </si>
   <si>
-    <t>char</t>
-  </si>
-  <si>
-    <t>varchar</t>
-  </si>
-  <si>
-    <t>item_sort</t>
-  </si>
-  <si>
-    <t>item_sort_code</t>
-  </si>
-  <si>
-    <t>item_sort_name</t>
-  </si>
-  <si>
-    <t>item_sort_description</t>
-  </si>
-  <si>
-    <t>物品分类表</t>
-  </si>
-  <si>
-    <t>物品分类编码</t>
-  </si>
-  <si>
-    <t>物品分类名称</t>
-  </si>
-  <si>
-    <t>物品分类描述</t>
-  </si>
-  <si>
-    <t>character</t>
-  </si>
-  <si>
-    <t>character_id</t>
-  </si>
-  <si>
-    <t>character_name</t>
-  </si>
-  <si>
-    <t>character_sex</t>
-  </si>
-  <si>
-    <t>character_age</t>
-  </si>
-  <si>
-    <t>character_race_id</t>
-  </si>
-  <si>
-    <t>character_description</t>
-  </si>
-  <si>
-    <t>角色</t>
-  </si>
-  <si>
-    <t>角色_id</t>
-  </si>
-  <si>
-    <t>角色名称</t>
-  </si>
-  <si>
-    <t>角色性别</t>
-  </si>
-  <si>
-    <t>角色年龄</t>
-  </si>
-  <si>
-    <t>角色种族id</t>
-  </si>
-  <si>
-    <t>角色描述</t>
-  </si>
-  <si>
-    <t>bool(tinyint(1))</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>race_sort</t>
   </si>
   <si>
-    <t>race_id</t>
-  </si>
-  <si>
     <t>race_code</t>
   </si>
   <si>
@@ -172,9 +207,6 @@
     <t>种族分类表</t>
   </si>
   <si>
-    <t>种族id</t>
-  </si>
-  <si>
     <t>种族编码</t>
   </si>
   <si>
@@ -182,6 +214,39 @@
   </si>
   <si>
     <t>种族描述</t>
+  </si>
+  <si>
+    <t>race_subspecies</t>
+  </si>
+  <si>
+    <t>race_subspecies_id</t>
+  </si>
+  <si>
+    <t>race_subspecies_code</t>
+  </si>
+  <si>
+    <t>race_subspecies_name</t>
+  </si>
+  <si>
+    <t>race_subspecies_description</t>
+  </si>
+  <si>
+    <t>亚种分类表</t>
+  </si>
+  <si>
+    <t>亚种编码</t>
+  </si>
+  <si>
+    <t>亚种名称</t>
+  </si>
+  <si>
+    <t>亚种描述</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>错误代码</t>
   </si>
 </sst>
 </file>
@@ -1115,19 +1180,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="10.5929203539823" customWidth="1"/>
-    <col min="2" max="2" width="13.929203539823" customWidth="1"/>
-    <col min="3" max="3" width="16.1946902654867" customWidth="1"/>
-    <col min="4" max="4" width="18.3893805309735" customWidth="1"/>
-    <col min="5" max="5" width="15.0619469026549" customWidth="1"/>
-    <col min="6" max="6" width="21.787610619469" customWidth="1"/>
-    <col min="7" max="7" width="23.9911504424779" customWidth="1"/>
-    <col min="8" max="8" width="11.3097345132743" customWidth="1"/>
-    <col min="9" max="9" width="13.929203539823" customWidth="1"/>
-    <col min="10" max="10" width="16.1946902654867" customWidth="1"/>
+    <col min="1" max="1" width="7.31858407079646" customWidth="1"/>
+    <col min="2" max="2" width="8.53097345132743" customWidth="1"/>
+    <col min="3" max="3" width="10.5929203539823" customWidth="1"/>
+    <col min="4" max="4" width="13.929203539823" customWidth="1"/>
+    <col min="5" max="5" width="10.5929203539823" customWidth="1"/>
+    <col min="6" max="6" width="18.3893805309735" customWidth="1"/>
+    <col min="7" max="8" width="12.7964601769912" customWidth="1"/>
+    <col min="9" max="10" width="10.5929203539823" customWidth="1"/>
     <col min="11" max="11" width="23.9911504424779" customWidth="1"/>
     <col min="13" max="13" width="10.5929203539823" customWidth="1"/>
     <col min="14" max="14" width="13.929203539823" customWidth="1"/>
@@ -1136,7 +1199,7 @@
     <col min="18" max="18" width="16.1946902654867" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1155,42 +1218,78 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1203,61 +1302,99 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="11.3097345132743" customWidth="1"/>
     <col min="2" max="2" width="13.929203539823" customWidth="1"/>
     <col min="3" max="4" width="16.1946902654867" customWidth="1"/>
     <col min="5" max="5" width="23.9911504424779" customWidth="1"/>
+    <col min="6" max="7" width="12.7964601769912" customWidth="1"/>
+    <col min="8" max="9" width="10.5929203539823" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:9">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1270,82 +1407,130 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="10.5929203539823" customWidth="1"/>
     <col min="2" max="2" width="13.929203539823" customWidth="1"/>
     <col min="3" max="3" width="16.1946902654867" customWidth="1"/>
     <col min="4" max="4" width="18.3893805309735" customWidth="1"/>
-    <col min="5" max="5" width="15.0619469026549" customWidth="1"/>
-    <col min="6" max="6" width="21.787610619469" customWidth="1"/>
-    <col min="7" max="7" width="23.9911504424779" customWidth="1"/>
+    <col min="5" max="5" width="9.24778761061947" customWidth="1"/>
+    <col min="6" max="6" width="9.53097345132743" customWidth="1"/>
+    <col min="7" max="7" width="15.0619469026549" customWidth="1"/>
+    <col min="8" max="8" width="23.9911504424779" customWidth="1"/>
+    <col min="9" max="10" width="12.7964601769912" customWidth="1"/>
+    <col min="11" max="12" width="10.5929203539823" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1358,61 +1543,225 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="11.3097345132743" customWidth="1"/>
-    <col min="2" max="2" width="9.53097345132743" customWidth="1"/>
+    <col min="2" max="2" width="8.53097345132743" customWidth="1"/>
     <col min="3" max="4" width="10.5929203539823" customWidth="1"/>
     <col min="5" max="5" width="18.3893805309735" customWidth="1"/>
+    <col min="6" max="7" width="12.7964601769912" customWidth="1"/>
+    <col min="8" max="9" width="10.5929203539823" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
       </c>
       <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="17.3274336283186" customWidth="1"/>
+    <col min="2" max="2" width="20.6548672566372" customWidth="1"/>
+    <col min="3" max="4" width="22.858407079646" customWidth="1"/>
+    <col min="5" max="5" width="30.716814159292" customWidth="1"/>
+    <col min="6" max="7" width="12.7964601769912" customWidth="1"/>
+    <col min="8" max="9" width="10.5929203539823" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
         <v>46</v>
       </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>67</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:9">
       <c r="B3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
